--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 23:45</t>
+    <t xml:space="preserve">2026-08-17 14:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:46</t>
+    <t xml:space="preserve">2026-08-17 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 19:38</t>
+    <t xml:space="preserve">2026-09-06 20:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
